--- a/computer_vision/course schedule.xlsx
+++ b/computer_vision/course schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\computer_vision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32581B73-166F-4D77-B432-39B254ED5F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCBE253-52B8-49F0-8221-536787BFC36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{F859C6BE-0D75-4E38-989D-5436D0978838}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="226">
   <si>
     <t>Unit</t>
   </si>
@@ -690,6 +690,30 @@
   </si>
   <si>
     <t>20/127</t>
+  </si>
+  <si>
+    <t>21/127</t>
+  </si>
+  <si>
+    <t>24/127</t>
+  </si>
+  <si>
+    <t>23/127</t>
+  </si>
+  <si>
+    <t>27/127</t>
+  </si>
+  <si>
+    <t>33/127</t>
+  </si>
+  <si>
+    <t>36/127</t>
+  </si>
+  <si>
+    <t>874 001</t>
+  </si>
+  <si>
+    <t>42/127</t>
   </si>
 </sst>
 </file>
@@ -740,13 +764,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1150,13 +1173,13 @@
       <c r="I1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s">
         <v>208</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" t="s">
         <v>204</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" t="s">
         <v>216</v>
       </c>
     </row>
@@ -1391,6 +1414,12 @@
       <c r="E12">
         <v>36</v>
       </c>
+      <c r="H12">
+        <v>20</v>
+      </c>
+      <c r="I12" t="s">
+        <v>218</v>
+      </c>
       <c r="L12">
         <v>21</v>
       </c>
@@ -1405,6 +1434,12 @@
       <c r="E13">
         <v>22</v>
       </c>
+      <c r="H13">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>220</v>
+      </c>
       <c r="L13">
         <v>22</v>
       </c>
@@ -1419,6 +1454,15 @@
       <c r="E14">
         <v>35</v>
       </c>
+      <c r="H14">
+        <v>23</v>
+      </c>
+      <c r="I14" t="s">
+        <v>219</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.50347222222222221</v>
+      </c>
       <c r="L14">
         <v>24</v>
       </c>
@@ -1439,6 +1483,12 @@
       <c r="E15">
         <v>33</v>
       </c>
+      <c r="H15">
+        <v>26</v>
+      </c>
+      <c r="I15" t="s">
+        <v>221</v>
+      </c>
       <c r="L15">
         <v>27</v>
       </c>
@@ -1487,6 +1537,13 @@
       <c r="E18">
         <v>11</v>
       </c>
+      <c r="H18">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>222</v>
+      </c>
+      <c r="J18" s="4"/>
       <c r="L18">
         <v>33</v>
       </c>
@@ -1507,6 +1564,15 @@
       <c r="G19" t="s">
         <v>203</v>
       </c>
+      <c r="H19">
+        <v>32</v>
+      </c>
+      <c r="I19" t="s">
+        <v>222</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="L19">
         <v>33</v>
       </c>
@@ -1527,6 +1593,12 @@
       <c r="E20">
         <v>24</v>
       </c>
+      <c r="H20">
+        <v>35</v>
+      </c>
+      <c r="I20" t="s">
+        <v>223</v>
+      </c>
       <c r="L20">
         <v>36</v>
       </c>
@@ -1581,6 +1653,15 @@
       <c r="G23" t="s">
         <v>69</v>
       </c>
+      <c r="H23" t="s">
+        <v>224</v>
+      </c>
+      <c r="I23" t="s">
+        <v>225</v>
+      </c>
+      <c r="J23" s="4">
+        <v>2.0833333333333332E-2</v>
+      </c>
       <c r="L23">
         <v>42</v>
       </c>
@@ -1594,6 +1675,12 @@
       </c>
       <c r="E24">
         <v>33</v>
+      </c>
+      <c r="I24" t="s">
+        <v>225</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0.54166666666666663</v>
       </c>
       <c r="L24">
         <v>42.9</v>

--- a/computer_vision/course schedule.xlsx
+++ b/computer_vision/course schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\computer_vision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCBE253-52B8-49F0-8221-536787BFC36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3ACB3C6-BEB6-43EC-B30D-4E7FB529F1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{F859C6BE-0D75-4E38-989D-5436D0978838}"/>
+    <workbookView xWindow="4980" yWindow="4732" windowWidth="16875" windowHeight="10523" xr2:uid="{F859C6BE-0D75-4E38-989D-5436D0978838}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="227">
   <si>
     <t>Unit</t>
   </si>
@@ -714,6 +714,9 @@
   </si>
   <si>
     <t>42/127</t>
+  </si>
+  <si>
+    <t>53-  13:20</t>
   </si>
 </sst>
 </file>
@@ -1750,6 +1753,9 @@
       <c r="G28" t="s">
         <v>83</v>
       </c>
+      <c r="L28">
+        <v>50</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
@@ -1761,6 +1767,9 @@
       <c r="E29">
         <v>39</v>
       </c>
+      <c r="L29">
+        <v>51</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
@@ -1771,6 +1780,9 @@
       </c>
       <c r="E30">
         <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">

--- a/computer_vision/course schedule.xlsx
+++ b/computer_vision/course schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\computer_vision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3ACB3C6-BEB6-43EC-B30D-4E7FB529F1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BD8F83-B5A2-41C5-ADB2-D341CCBF0F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="4732" windowWidth="16875" windowHeight="10523" xr2:uid="{F859C6BE-0D75-4E38-989D-5436D0978838}"/>
+    <workbookView xWindow="3128" yWindow="3128" windowWidth="16875" windowHeight="10522" xr2:uid="{F859C6BE-0D75-4E38-989D-5436D0978838}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1801,6 +1801,9 @@
       <c r="E31">
         <v>27</v>
       </c>
+      <c r="L31">
+        <v>54.5</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C32" t="s">
@@ -1812,8 +1815,11 @@
       <c r="E32">
         <v>16</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="L32">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -1830,7 +1836,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C34" t="s">
         <v>97</v>
       </c>
@@ -1840,8 +1846,11 @@
       <c r="E34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="L34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>99</v>
       </c>
@@ -1858,7 +1867,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>102</v>
       </c>
@@ -1875,7 +1884,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>105</v>
       </c>
@@ -1892,7 +1901,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>108</v>
       </c>
@@ -1915,7 +1924,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>114</v>
       </c>
@@ -1932,7 +1941,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C40" t="s">
         <v>118</v>
       </c>
@@ -1943,7 +1952,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C41" t="s">
         <v>120</v>
       </c>
@@ -1954,7 +1963,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C42" t="s">
         <v>122</v>
       </c>
@@ -1965,7 +1974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>124</v>
       </c>
@@ -1982,7 +1991,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>127</v>
       </c>
@@ -1999,7 +2008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C45" t="s">
         <v>131</v>
       </c>
@@ -2010,7 +2019,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>133</v>
       </c>
@@ -2033,7 +2042,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C47" t="s">
         <v>139</v>
       </c>
@@ -2044,7 +2053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C48" t="s">
         <v>141</v>
       </c>

--- a/computer_vision/course schedule.xlsx
+++ b/computer_vision/course schedule.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\computer_vision\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C74C8F-56F1-4544-A2C6-CD119577D0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -700,19 +706,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -751,73 +762,69 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="20" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="20" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="20" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L70" displayName="Table1" name="Table1" id="1" totalsRowShown="0">
-  <autoFilter ref="A1:L70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:L70" totalsRowShown="0">
+  <autoFilter ref="A1:L70" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
-    <tableColumn name="Unit" id="1"/>
-    <tableColumn name="Title" id="2"/>
-    <tableColumn name="Lesson" id="3"/>
-    <tableColumn name="Topic" id="4"/>
-    <tableColumn name="Duration" id="5"/>
-    <tableColumn name="Problem Set" id="6"/>
-    <tableColumn name="Assignment" id="7"/>
-    <tableColumn name="# Video" id="8"/>
-    <tableColumn name="video number in playlist" id="9"/>
-    <tableColumn name="exact time" id="10"/>
-    <tableColumn name="Column1" id="11"/>
-    <tableColumn name="yael vid#" id="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Unit"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Title"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Lesson"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Topic"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Duration"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Problem Set"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Assignment"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="# Video"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="video number in playlist"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="exact time"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Column1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="yael vid#"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -826,10 +833,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -867,71 +874,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -959,7 +966,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -982,11 +989,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -995,13 +1002,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1011,7 +1018,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1020,7 +1027,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1029,7 +1036,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1037,10 +1044,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1105,1724 +1112,1402 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="9" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="31.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="31.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="18.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="10" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>42</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>1</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
+      <c r="J2" s="3"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>44</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>2</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1" t="s">
+      <c r="J3" s="3"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>24</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
       <c r="H4" s="7">
         <v>7.5</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1" t="s">
+      <c r="J4" s="3"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>34</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>8</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
+      <c r="J5" s="3"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>13</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>11</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J6" s="8">
-        <v>1.2773148148148148</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1" t="s">
+        <v>2.2768518518518519</v>
+      </c>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>27</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>12</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+      <c r="J7" s="3"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C8" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>19</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>14</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>35</v>
       </c>
       <c r="J8" s="8">
-        <v>1.2530092592592592</v>
-      </c>
-      <c r="K8" s="1" t="s">
+        <v>2.2525462962962965</v>
+      </c>
+      <c r="K8" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="1" t="s">
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>36</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>16</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>43</v>
       </c>
       <c r="J9" s="8">
-        <v>1.2078703703703704</v>
-      </c>
-      <c r="K9" s="1" t="s">
+        <v>2.2074074074074073</v>
+      </c>
+      <c r="K9" t="s">
         <v>44</v>
       </c>
-      <c r="L9" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C10" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>13</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>18</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" t="s">
         <v>47</v>
       </c>
       <c r="J10" s="8">
-        <v>1.1314814814814815</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
+        <v>2.1310185185185184</v>
+      </c>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C11" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>16</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>19</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>50</v>
       </c>
       <c r="J11" s="8">
-        <v>1.0273148148148148</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="1" t="s">
+        <v>2.0268518518518519</v>
+      </c>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>36</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>20</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="5">
+      <c r="J12" s="3"/>
+      <c r="L12" s="4">
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
+    <row r="13" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>22</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>22</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" t="s">
         <v>58</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="5">
+      <c r="J13" s="3"/>
+      <c r="L13" s="4">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
+    <row r="14" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C14" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>35</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>23</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" t="s">
         <v>61</v>
       </c>
       <c r="J14" s="8">
-        <v>1.5030092592592592</v>
-      </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="5">
+        <v>2.5025462962962965</v>
+      </c>
+      <c r="L14" s="4">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>33</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>26</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>66</v>
       </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="5">
+      <c r="J15" s="3"/>
+      <c r="L15" s="4">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1" t="s">
+    <row r="16" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C16" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>26</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="5">
+      <c r="H16" s="6"/>
+      <c r="J16" s="3"/>
+      <c r="L16" s="4">
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>26</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="5">
+      <c r="H17" s="6"/>
+      <c r="J17" s="3"/>
+      <c r="L17" s="4">
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1" t="s">
+    <row r="18" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C18" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>11</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>32</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" t="s">
         <v>74</v>
       </c>
       <c r="J18" s="8"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="5">
+      <c r="L18" s="4">
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1" t="s">
+    <row r="19" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C19" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>29</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>32</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" t="s">
         <v>74</v>
       </c>
       <c r="J19" s="8">
-        <v>1.5412037037037036</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="5">
+        <v>2.5407407407407407</v>
+      </c>
+      <c r="L19" s="4">
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>24</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>35</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" t="s">
         <v>83</v>
       </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="5">
+      <c r="J20" s="3"/>
+      <c r="L20" s="4">
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1" t="s">
+    <row r="21" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C21" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>16</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="5">
+      <c r="H21" s="6"/>
+      <c r="J21" s="3"/>
+      <c r="L21" s="4">
         <v>37</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1" t="s">
+    <row r="22" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C22" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>31</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="5">
+      <c r="H22" s="6"/>
+      <c r="J22" s="3"/>
+      <c r="L22" s="4">
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>10</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>93</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" t="s">
         <v>95</v>
       </c>
       <c r="J23" s="8">
-        <v>1.0203703703703704</v>
-      </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="5">
+        <v>2.0199074074074073</v>
+      </c>
+      <c r="L23" s="4">
         <v>42</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1" t="s">
+    <row r="24" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C24" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>33</v>
       </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="1" t="s">
+      <c r="H24" s="6"/>
+      <c r="I24" t="s">
         <v>95</v>
       </c>
       <c r="J24" s="8">
-        <v>1.5412037037037036</v>
-      </c>
-      <c r="K24" s="1"/>
+        <v>2.5407407407407407</v>
+      </c>
       <c r="L24" s="7">
         <v>42.9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1" t="s">
+    <row r="25" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C25" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>14</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="5">
+      <c r="H25" s="6"/>
+      <c r="J25" s="3"/>
+      <c r="L25" s="4">
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1" t="s">
+    <row r="26" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C26" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>22</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="5">
+      <c r="H26" s="6"/>
+      <c r="J26" s="3"/>
+      <c r="L26" s="4">
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1" t="s">
+    <row r="27" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C27" t="s">
         <v>102</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>37</v>
       </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="1"/>
+      <c r="H27" s="6"/>
+      <c r="J27" s="3"/>
       <c r="L27" s="7">
         <v>47.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>107</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>13</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>109</v>
       </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="5">
+      <c r="H28" s="6"/>
+      <c r="J28" s="3"/>
+      <c r="L28" s="4">
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1" t="s">
+    <row r="29" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C29" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>111</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>39</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="5">
+      <c r="H29" s="6"/>
+      <c r="J29" s="3"/>
+      <c r="L29" s="4">
         <v>51</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1" t="s">
+    <row r="30" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C30" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>23</v>
       </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="2" t="s">
+      <c r="H30" s="6"/>
+      <c r="J30" s="3"/>
+      <c r="L30" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
         <v>115</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>117</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>118</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="4">
         <v>27</v>
       </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="1"/>
+      <c r="H31" s="6"/>
+      <c r="J31" s="3"/>
       <c r="L31" s="7">
         <v>54.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1" t="s">
+    <row r="32" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C32" t="s">
         <v>119</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>16</v>
       </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="5">
+      <c r="H32" s="6"/>
+      <c r="J32" s="3"/>
+      <c r="L32" s="4">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
         <v>121</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="4">
         <v>31</v>
       </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1" t="s">
+      <c r="H33" s="6"/>
+      <c r="J33" s="3"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C34" t="s">
         <v>124</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>125</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="4">
         <v>33</v>
       </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="5">
+      <c r="H34" s="6"/>
+      <c r="J34" s="3"/>
+      <c r="L34" s="4">
         <v>60</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
         <v>126</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>127</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>128</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="4">
         <v>35</v>
       </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="1" t="s">
+      <c r="H35" s="6"/>
+      <c r="J35" s="3"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>131</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s">
         <v>130</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="4">
         <v>26</v>
       </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="1" t="s">
+      <c r="H36" s="6"/>
+      <c r="J36" s="3"/>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
         <v>132</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" t="s">
         <v>133</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="4">
         <v>34</v>
       </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="1" t="s">
+      <c r="H37" s="6"/>
+      <c r="J37" s="3"/>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
         <v>135</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s">
         <v>138</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="4">
         <v>16</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" t="s">
         <v>140</v>
       </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="1" t="s">
+      <c r="H38" s="6"/>
+      <c r="J38" s="3"/>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>142</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>143</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s">
         <v>144</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="4">
         <v>24</v>
       </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1" t="s">
+      <c r="H39" s="6"/>
+      <c r="J39" s="3"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C40" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" t="s">
         <v>146</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="4">
         <v>17</v>
       </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1" t="s">
+      <c r="H40" s="6"/>
+      <c r="J40" s="3"/>
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C41" t="s">
         <v>147</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s">
         <v>148</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="4">
         <v>33</v>
       </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1" t="s">
+      <c r="H41" s="6"/>
+      <c r="J41" s="3"/>
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C42" t="s">
         <v>149</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s">
         <v>150</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="4">
         <v>24</v>
       </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="1" t="s">
+      <c r="H42" s="6"/>
+      <c r="J42" s="3"/>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
         <v>151</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>152</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>153</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" t="s">
         <v>152</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="4">
         <v>14</v>
       </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="1" t="s">
+      <c r="H43" s="6"/>
+      <c r="J43" s="3"/>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
         <v>154</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>155</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>156</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" t="s">
         <v>157</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="4">
         <v>21</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1" t="s">
+      <c r="H44" s="6"/>
+      <c r="J44" s="3"/>
+      <c r="L44" s="6"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C45" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" t="s">
         <v>159</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="4">
         <v>36</v>
       </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="1" t="s">
+      <c r="H45" s="6"/>
+      <c r="J45" s="3"/>
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
         <v>160</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>161</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>162</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" t="s">
         <v>163</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="4">
         <v>23</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" t="s">
         <v>165</v>
       </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1" t="s">
+      <c r="H46" s="6"/>
+      <c r="J46" s="3"/>
+      <c r="L46" s="6"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C47" t="s">
         <v>166</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" t="s">
         <v>167</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="4">
         <v>17</v>
       </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1" t="s">
+      <c r="H47" s="6"/>
+      <c r="J47" s="3"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C48" t="s">
         <v>168</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" t="s">
         <v>169</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="4">
         <v>24</v>
       </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1" t="s">
+      <c r="H48" s="6"/>
+      <c r="J48" s="3"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C49" t="s">
         <v>170</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" t="s">
         <v>171</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="4">
         <v>15</v>
       </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="1" t="s">
+      <c r="H49" s="6"/>
+      <c r="J49" s="3"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
         <v>172</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>174</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" t="s">
         <v>173</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="4">
         <v>27</v>
       </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75" hidden="1">
-      <c r="A51" s="1" t="s">
+      <c r="H50" s="6"/>
+      <c r="J50" s="3"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
         <v>175</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>176</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>177</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" t="s">
         <v>176</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="4">
         <v>21</v>
       </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75" hidden="1">
-      <c r="A52" s="1" t="s">
+      <c r="H51" s="6"/>
+      <c r="J51" s="3"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
         <v>178</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
         <v>179</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>180</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" t="s">
         <v>179</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="4">
         <v>28</v>
       </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75" hidden="1">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1" t="s">
+      <c r="H52" s="6"/>
+      <c r="J52" s="3"/>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C53" t="s">
         <v>181</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" t="s">
         <v>182</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="4">
         <v>48</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75" hidden="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1" t="s">
+      <c r="H53" s="6"/>
+      <c r="J53" s="3"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C54" t="s">
         <v>183</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" t="s">
         <v>184</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="4">
         <v>26</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75" hidden="1">
-      <c r="A55" s="1" t="s">
+      <c r="H54" s="6"/>
+      <c r="J54" s="3"/>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
         <v>185</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
         <v>186</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>187</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" t="s">
         <v>186</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="4">
         <v>27</v>
       </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75" hidden="1">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1" t="s">
+      <c r="H55" s="6"/>
+      <c r="J55" s="3"/>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C56" t="s">
         <v>188</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" t="s">
         <v>189</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="4">
         <v>27</v>
       </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75" hidden="1">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1" t="s">
+      <c r="H56" s="6"/>
+      <c r="J56" s="3"/>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C57" t="s">
         <v>190</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" t="s">
         <v>191</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="4">
         <v>51</v>
       </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75" hidden="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1" t="s">
+      <c r="H57" s="6"/>
+      <c r="J57" s="3"/>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C58" t="s">
         <v>192</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" t="s">
         <v>193</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="4">
         <v>14</v>
       </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75" hidden="1">
-      <c r="A59" s="1" t="s">
+      <c r="H58" s="6"/>
+      <c r="J58" s="3"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
         <v>194</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" t="s">
         <v>195</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>196</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" t="s">
         <v>197</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="4">
         <v>24</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" t="s">
         <v>198</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" t="s">
         <v>199</v>
       </c>
-      <c r="H59" s="2"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75" hidden="1">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1" t="s">
+      <c r="H59" s="6"/>
+      <c r="J59" s="3"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C60" t="s">
         <v>200</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" t="s">
         <v>201</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="4">
         <v>32</v>
       </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75" hidden="1">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1" t="s">
+      <c r="H60" s="6"/>
+      <c r="J60" s="3"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C61" t="s">
         <v>202</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" t="s">
         <v>203</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="4">
         <v>46</v>
       </c>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75" hidden="1">
-      <c r="A62" s="1" t="s">
+      <c r="H61" s="6"/>
+      <c r="J61" s="3"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
         <v>204</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
         <v>205</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>206</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" t="s">
         <v>207</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="4">
         <v>36</v>
       </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75" hidden="1">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1" t="s">
+      <c r="H62" s="6"/>
+      <c r="J62" s="3"/>
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C63" t="s">
         <v>208</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" t="s">
         <v>209</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="4">
         <v>18</v>
       </c>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75" hidden="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1" t="s">
+      <c r="H63" s="6"/>
+      <c r="J63" s="3"/>
+      <c r="L63" s="6"/>
+    </row>
+    <row r="64" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C64" t="s">
         <v>210</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" t="s">
         <v>211</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="4">
         <v>18</v>
       </c>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75" hidden="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1" t="s">
+      <c r="H64" s="6"/>
+      <c r="J64" s="3"/>
+      <c r="L64" s="6"/>
+    </row>
+    <row r="65" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C65" t="s">
         <v>212</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" t="s">
         <v>213</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E65" s="4">
         <v>13</v>
       </c>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="1" t="s">
+      <c r="H65" s="6"/>
+      <c r="J65" s="3"/>
+      <c r="L65" s="6"/>
+    </row>
+    <row r="66" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
         <v>214</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" t="s">
         <v>215</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" t="s">
         <v>216</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" t="s">
         <v>215</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E66" s="4">
         <v>37</v>
       </c>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75" hidden="1">
-      <c r="A67" s="1" t="s">
+      <c r="H66" s="6"/>
+      <c r="J66" s="3"/>
+      <c r="L66" s="6"/>
+    </row>
+    <row r="67" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
         <v>217</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" t="s">
         <v>218</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" t="s">
         <v>219</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" t="s">
         <v>218</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E67" s="4">
         <v>34</v>
       </c>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75" hidden="1">
-      <c r="A68" s="1" t="s">
+      <c r="H67" s="6"/>
+      <c r="J67" s="3"/>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
         <v>220</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" t="s">
         <v>221</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" t="s">
         <v>222</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" t="s">
         <v>221</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E68" s="4">
         <v>38</v>
       </c>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75" hidden="1">
-      <c r="A69" s="1" t="s">
+      <c r="H68" s="6"/>
+      <c r="J68" s="3"/>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
         <v>223</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" t="s">
         <v>224</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" t="s">
         <v>225</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" t="s">
         <v>224</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="4">
         <v>27</v>
       </c>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75" hidden="1">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1" t="s">
+      <c r="H69" s="6"/>
+      <c r="J69" s="3"/>
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
         <v>226</v>
       </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="2"/>
+      <c r="E70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="J70" s="3"/>
+      <c r="L70" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/computer_vision/course schedule.xlsx
+++ b/computer_vision/course schedule.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\computer_vision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C74C8F-56F1-4544-A2C6-CD119577D0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2D0081-36B2-40E1-9F14-1359C78B7783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2062" yWindow="2835" windowWidth="16876" windowHeight="10418" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="228">
   <si>
     <t>Unit</t>
   </si>
@@ -701,6 +714,9 @@
   </si>
   <si>
     <t>Final Exam (T-Square)</t>
+  </si>
+  <si>
+    <t>74 - 7:30</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1918,9 @@
       </c>
       <c r="H35" s="6"/>
       <c r="J35" s="3"/>
-      <c r="L35" s="6"/>
+      <c r="L35" s="6">
+        <v>62</v>
+      </c>
     </row>
     <row r="36" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
@@ -2030,7 +2048,9 @@
       </c>
       <c r="H42" s="6"/>
       <c r="J42" s="3"/>
-      <c r="L42" s="6"/>
+      <c r="L42" s="6" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="43" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">

--- a/computer_vision/course schedule.xlsx
+++ b/computer_vision/course schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\computer_vision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2D0081-36B2-40E1-9F14-1359C78B7783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA68CBC8-8776-4F4C-9678-9C0EEC6A52AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2062" yWindow="2835" windowWidth="16876" windowHeight="10418" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="3173" windowWidth="16875" windowHeight="10417" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2130,7 +2130,9 @@
       </c>
       <c r="H46" s="6"/>
       <c r="J46" s="3"/>
-      <c r="L46" s="6"/>
+      <c r="L46" s="6">
+        <v>83</v>
+      </c>
     </row>
     <row r="47" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" t="s">
@@ -2192,7 +2194,9 @@
       </c>
       <c r="H50" s="6"/>
       <c r="J50" s="3"/>
-      <c r="L50" s="6"/>
+      <c r="L50" s="6">
+        <v>87</v>
+      </c>
     </row>
     <row r="51" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">

--- a/computer_vision/course schedule.xlsx
+++ b/computer_vision/course schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ron Tohar\Desktop\הכשרה\CV_training\computer_vision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA68CBC8-8776-4F4C-9678-9C0EEC6A52AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFBA225-E65D-4F52-8AEE-F8126A98E6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="3173" windowWidth="16875" windowHeight="10417" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="225">
   <si>
     <t>Unit</t>
   </si>
@@ -65,9 +65,6 @@
     <t>exact time</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
     <t>yael vid#</t>
   </si>
   <si>
@@ -143,9 +140,6 @@
     <t>15/127</t>
   </si>
   <si>
-    <t>בתכלס מדבר על זה בעיקר בסרטון אחרי זה (15) בדקה 5:40</t>
-  </si>
-  <si>
     <t>2B</t>
   </si>
   <si>
@@ -165,9 +159,6 @@
   </si>
   <si>
     <t>17/127</t>
-  </si>
-  <si>
-    <t>מתחיל מסוף סרטון קודם הסברים אבל המילה hough transform מופיעה איפה שכתבתי פעם ראשונה</t>
   </si>
   <si>
     <t>2B-L2</t>
@@ -824,9 +815,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:L70" totalsRowShown="0">
-  <autoFilter ref="A1:L70" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:K70" totalsRowShown="0">
+  <autoFilter ref="A1:K70" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Unit"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Title"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Lesson"/>
@@ -837,7 +828,6 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="# Video"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="video number in playlist"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="exact time"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Column1"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="yael vid#"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1132,7 +1122,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
@@ -1145,11 +1135,10 @@
     <col min="8" max="8" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.5625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1180,53 +1169,50 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4">
         <v>42</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
       </c>
       <c r="H2" s="4">
         <v>1</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
       <c r="E3" s="4">
         <v>44</v>
@@ -1235,14 +1221,14 @@
         <v>2</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
         <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
       </c>
       <c r="E4" s="4">
         <v>24</v>
@@ -1251,17 +1237,17 @@
         <v>7.5</v>
       </c>
       <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
       </c>
       <c r="E5" s="4">
         <v>34</v>
@@ -1270,17 +1256,17 @@
         <v>8</v>
       </c>
       <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
       </c>
       <c r="E6" s="4">
         <v>13</v>
@@ -1289,19 +1275,19 @@
         <v>11</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J6" s="8">
         <v>2.2768518518518519</v>
       </c>
-      <c r="L6" s="6"/>
-    </row>
-    <row r="7" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
         <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
       </c>
       <c r="E7" s="4">
         <v>27</v>
@@ -1310,17 +1296,17 @@
         <v>12</v>
       </c>
       <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
       </c>
       <c r="E8" s="4">
         <v>19</v>
@@ -1329,58 +1315,52 @@
         <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J8" s="8">
         <v>2.2525462962962965</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
       </c>
       <c r="E9" s="4">
         <v>36</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H9" s="4">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J9" s="8">
         <v>2.2074074074074073</v>
       </c>
-      <c r="K9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4">
         <v>13</v>
@@ -1389,19 +1369,19 @@
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J10" s="8">
         <v>2.1310185185185184</v>
       </c>
-      <c r="L10" s="6"/>
-    </row>
-    <row r="11" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E11" s="4">
         <v>16</v>
@@ -1410,25 +1390,25 @@
         <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J11" s="8">
         <v>2.0268518518518519</v>
       </c>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
         <v>51</v>
-      </c>
-      <c r="B12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
       </c>
       <c r="E12" s="4">
         <v>36</v>
@@ -1437,19 +1417,19 @@
         <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="L12" s="4">
+      <c r="K12" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E13" s="4">
         <v>22</v>
@@ -1458,19 +1438,19 @@
         <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="L13" s="4">
+      <c r="K13" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E14" s="4">
         <v>35</v>
@@ -1479,27 +1459,27 @@
         <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J14" s="8">
         <v>2.5025462962962965</v>
       </c>
-      <c r="L14" s="4">
+      <c r="K14" s="4">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
         <v>62</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
       </c>
       <c r="E15" s="4">
         <v>33</v>
@@ -1508,57 +1488,57 @@
         <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="L15" s="4">
+      <c r="K15" s="4">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E16" s="4">
         <v>26</v>
       </c>
       <c r="H16" s="6"/>
       <c r="J16" s="3"/>
-      <c r="L16" s="4">
+      <c r="K16" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E17" s="4">
         <v>26</v>
       </c>
       <c r="H17" s="6"/>
       <c r="J17" s="3"/>
-      <c r="L17" s="4">
+      <c r="K17" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E18" s="4">
         <v>11</v>
@@ -1567,54 +1547,54 @@
         <v>32</v>
       </c>
       <c r="I18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J18" s="8"/>
-      <c r="L18" s="4">
+      <c r="K18" s="4">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E19" s="4">
         <v>29</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H19" s="4">
         <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J19" s="8">
         <v>2.5407407407407407</v>
       </c>
-      <c r="L19" s="4">
+      <c r="K19" s="4">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
         <v>79</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
       </c>
       <c r="E20" s="4">
         <v>24</v>
@@ -1623,915 +1603,915 @@
         <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J20" s="3"/>
-      <c r="L20" s="4">
+      <c r="K20" s="4">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E21" s="4">
         <v>16</v>
       </c>
       <c r="H21" s="6"/>
       <c r="J21" s="3"/>
-      <c r="L21" s="4">
+      <c r="K21" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E22" s="4">
         <v>31</v>
       </c>
       <c r="H22" s="6"/>
       <c r="J22" s="3"/>
-      <c r="L22" s="4">
+      <c r="K22" s="4">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" t="s">
         <v>88</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" t="s">
-        <v>91</v>
       </c>
       <c r="E23" s="4">
         <v>10</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" t="s">
         <v>92</v>
-      </c>
-      <c r="G23" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" t="s">
-        <v>95</v>
       </c>
       <c r="J23" s="8">
         <v>2.0199074074074073</v>
       </c>
-      <c r="L23" s="4">
+      <c r="K23" s="4">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E24" s="4">
         <v>33</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J24" s="8">
         <v>2.5407407407407407</v>
       </c>
-      <c r="L24" s="7">
+      <c r="K24" s="7">
         <v>42.9</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E25" s="4">
         <v>14</v>
       </c>
       <c r="H25" s="6"/>
       <c r="J25" s="3"/>
-      <c r="L25" s="4">
+      <c r="K25" s="4">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E26" s="4">
         <v>22</v>
       </c>
       <c r="H26" s="6"/>
       <c r="J26" s="3"/>
-      <c r="L26" s="4">
+      <c r="K26" s="4">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E27" s="4">
         <v>37</v>
       </c>
       <c r="H27" s="6"/>
       <c r="J27" s="3"/>
-      <c r="L27" s="7">
+      <c r="K27" s="7">
         <v>47.5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" t="s">
         <v>104</v>
-      </c>
-      <c r="B28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" t="s">
-        <v>107</v>
       </c>
       <c r="E28" s="4">
         <v>13</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G28" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H28" s="6"/>
       <c r="J28" s="3"/>
-      <c r="L28" s="4">
+      <c r="K28" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E29" s="4">
         <v>39</v>
       </c>
       <c r="H29" s="6"/>
       <c r="J29" s="3"/>
-      <c r="L29" s="4">
+      <c r="K29" s="4">
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E30" s="4">
         <v>23</v>
       </c>
       <c r="H30" s="6"/>
       <c r="J30" s="3"/>
-      <c r="L30" s="1" t="s">
+      <c r="K30" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
+      <c r="D31" t="s">
         <v>115</v>
-      </c>
-      <c r="B31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
       </c>
       <c r="E31" s="4">
         <v>27</v>
       </c>
       <c r="H31" s="6"/>
       <c r="J31" s="3"/>
-      <c r="L31" s="7">
+      <c r="K31" s="7">
         <v>54.5</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E32" s="4">
         <v>16</v>
       </c>
       <c r="H32" s="6"/>
       <c r="J32" s="3"/>
-      <c r="L32" s="4">
+      <c r="K32" s="4">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E33" s="4">
         <v>31</v>
       </c>
       <c r="H33" s="6"/>
       <c r="J33" s="3"/>
-      <c r="L33" s="6"/>
-    </row>
-    <row r="34" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K33" s="6"/>
+    </row>
+    <row r="34" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E34" s="4">
         <v>33</v>
       </c>
       <c r="H34" s="6"/>
       <c r="J34" s="3"/>
-      <c r="L34" s="4">
+      <c r="K34" s="4">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E35" s="4">
         <v>35</v>
       </c>
       <c r="H35" s="6"/>
       <c r="J35" s="3"/>
-      <c r="L35" s="6">
+      <c r="K35" s="6">
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E36" s="4">
         <v>26</v>
       </c>
       <c r="H36" s="6"/>
       <c r="J36" s="3"/>
-      <c r="L36" s="6"/>
-    </row>
-    <row r="37" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K36" s="6"/>
+    </row>
+    <row r="37" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E37" s="4">
         <v>34</v>
       </c>
       <c r="H37" s="6"/>
       <c r="J37" s="3"/>
-      <c r="L37" s="6"/>
-    </row>
-    <row r="38" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K37" s="6"/>
+    </row>
+    <row r="38" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" t="s">
         <v>135</v>
-      </c>
-      <c r="B38" t="s">
-        <v>136</v>
-      </c>
-      <c r="C38" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" t="s">
-        <v>138</v>
       </c>
       <c r="E38" s="4">
         <v>16</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H38" s="6"/>
       <c r="J38" s="3"/>
-      <c r="L38" s="6"/>
-    </row>
-    <row r="39" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K38" s="6"/>
+    </row>
+    <row r="39" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
+        <v>138</v>
+      </c>
+      <c r="B39" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" t="s">
         <v>141</v>
-      </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-      <c r="C39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D39" t="s">
-        <v>144</v>
       </c>
       <c r="E39" s="4">
         <v>24</v>
       </c>
       <c r="H39" s="6"/>
       <c r="J39" s="3"/>
-      <c r="L39" s="6"/>
-    </row>
-    <row r="40" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K39" s="6"/>
+    </row>
+    <row r="40" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E40" s="4">
         <v>17</v>
       </c>
       <c r="H40" s="6"/>
       <c r="J40" s="3"/>
-      <c r="L40" s="6"/>
-    </row>
-    <row r="41" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K40" s="6"/>
+    </row>
+    <row r="41" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E41" s="4">
         <v>33</v>
       </c>
       <c r="H41" s="6"/>
       <c r="J41" s="3"/>
-      <c r="L41" s="6"/>
-    </row>
-    <row r="42" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K41" s="6"/>
+    </row>
+    <row r="42" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E42" s="4">
         <v>24</v>
       </c>
       <c r="H42" s="6"/>
       <c r="J42" s="3"/>
-      <c r="L42" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K42" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D43" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E43" s="4">
         <v>14</v>
       </c>
       <c r="H43" s="6"/>
       <c r="J43" s="3"/>
-      <c r="L43" s="6"/>
-    </row>
-    <row r="44" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K43" s="6"/>
+    </row>
+    <row r="44" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" t="s">
+        <v>152</v>
+      </c>
+      <c r="C44" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" t="s">
         <v>154</v>
-      </c>
-      <c r="B44" t="s">
-        <v>155</v>
-      </c>
-      <c r="C44" t="s">
-        <v>156</v>
-      </c>
-      <c r="D44" t="s">
-        <v>157</v>
       </c>
       <c r="E44" s="4">
         <v>21</v>
       </c>
       <c r="H44" s="6"/>
       <c r="J44" s="3"/>
-      <c r="L44" s="6"/>
-    </row>
-    <row r="45" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K44" s="6"/>
+    </row>
+    <row r="45" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D45" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E45" s="4">
         <v>36</v>
       </c>
       <c r="H45" s="6"/>
       <c r="J45" s="3"/>
-      <c r="L45" s="6"/>
-    </row>
-    <row r="46" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K45" s="6"/>
+    </row>
+    <row r="46" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" t="s">
         <v>160</v>
-      </c>
-      <c r="B46" t="s">
-        <v>161</v>
-      </c>
-      <c r="C46" t="s">
-        <v>162</v>
-      </c>
-      <c r="D46" t="s">
-        <v>163</v>
       </c>
       <c r="E46" s="4">
         <v>23</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G46" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H46" s="6"/>
       <c r="J46" s="3"/>
-      <c r="L46" s="6">
+      <c r="K46" s="6">
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D47" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E47" s="4">
         <v>17</v>
       </c>
       <c r="H47" s="6"/>
       <c r="J47" s="3"/>
-      <c r="L47" s="6"/>
-    </row>
-    <row r="48" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K47" s="6"/>
+    </row>
+    <row r="48" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E48" s="4">
         <v>24</v>
       </c>
       <c r="H48" s="6"/>
       <c r="J48" s="3"/>
-      <c r="L48" s="6"/>
-    </row>
-    <row r="49" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K48" s="6"/>
+    </row>
+    <row r="49" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D49" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E49" s="4">
         <v>15</v>
       </c>
       <c r="H49" s="6"/>
       <c r="J49" s="3"/>
-      <c r="L49" s="6"/>
-    </row>
-    <row r="50" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K49" s="6"/>
+    </row>
+    <row r="50" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B50" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C50" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D50" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E50" s="4">
         <v>27</v>
       </c>
       <c r="H50" s="6"/>
       <c r="J50" s="3"/>
-      <c r="L50" s="6">
+      <c r="K50" s="6">
         <v>87</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B51" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C51" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D51" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E51" s="4">
         <v>21</v>
       </c>
       <c r="H51" s="6"/>
       <c r="J51" s="3"/>
-      <c r="L51" s="6"/>
-    </row>
-    <row r="52" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K51" s="6"/>
+    </row>
+    <row r="52" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E52" s="4">
         <v>28</v>
       </c>
       <c r="H52" s="6"/>
       <c r="J52" s="3"/>
-      <c r="L52" s="6"/>
-    </row>
-    <row r="53" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K52" s="6"/>
+    </row>
+    <row r="53" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D53" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E53" s="4">
         <v>48</v>
       </c>
       <c r="H53" s="6"/>
       <c r="J53" s="3"/>
-      <c r="L53" s="6"/>
-    </row>
-    <row r="54" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K53" s="6"/>
+    </row>
+    <row r="54" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D54" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E54" s="4">
         <v>26</v>
       </c>
       <c r="H54" s="6"/>
       <c r="J54" s="3"/>
-      <c r="L54" s="6"/>
-    </row>
-    <row r="55" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K54" s="6"/>
+    </row>
+    <row r="55" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B55" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C55" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D55" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E55" s="4">
         <v>27</v>
       </c>
       <c r="H55" s="6"/>
       <c r="J55" s="3"/>
-      <c r="L55" s="6"/>
-    </row>
-    <row r="56" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K55" s="6"/>
+    </row>
+    <row r="56" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D56" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E56" s="4">
         <v>27</v>
       </c>
       <c r="H56" s="6"/>
       <c r="J56" s="3"/>
-      <c r="L56" s="6"/>
-    </row>
-    <row r="57" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K56" s="6"/>
+    </row>
+    <row r="57" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D57" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E57" s="4">
         <v>51</v>
       </c>
       <c r="H57" s="6"/>
       <c r="J57" s="3"/>
-      <c r="L57" s="6"/>
-    </row>
-    <row r="58" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K57" s="6"/>
+    </row>
+    <row r="58" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D58" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E58" s="4">
         <v>14</v>
       </c>
       <c r="H58" s="6"/>
       <c r="J58" s="3"/>
-      <c r="L58" s="6"/>
-    </row>
-    <row r="59" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K58" s="6"/>
+    </row>
+    <row r="59" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
+        <v>191</v>
+      </c>
+      <c r="B59" t="s">
+        <v>192</v>
+      </c>
+      <c r="C59" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59" t="s">
         <v>194</v>
-      </c>
-      <c r="B59" t="s">
-        <v>195</v>
-      </c>
-      <c r="C59" t="s">
-        <v>196</v>
-      </c>
-      <c r="D59" t="s">
-        <v>197</v>
       </c>
       <c r="E59" s="4">
         <v>24</v>
       </c>
       <c r="F59" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G59" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H59" s="6"/>
       <c r="J59" s="3"/>
-      <c r="L59" s="6"/>
-    </row>
-    <row r="60" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K59" s="6"/>
+    </row>
+    <row r="60" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D60" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E60" s="4">
         <v>32</v>
       </c>
       <c r="H60" s="6"/>
       <c r="J60" s="3"/>
-      <c r="L60" s="6"/>
-    </row>
-    <row r="61" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K60" s="6"/>
+    </row>
+    <row r="61" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D61" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E61" s="4">
         <v>46</v>
       </c>
       <c r="H61" s="6"/>
       <c r="J61" s="3"/>
-      <c r="L61" s="6"/>
-    </row>
-    <row r="62" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K61" s="6"/>
+    </row>
+    <row r="62" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
+        <v>201</v>
+      </c>
+      <c r="B62" t="s">
+        <v>202</v>
+      </c>
+      <c r="C62" t="s">
+        <v>203</v>
+      </c>
+      <c r="D62" t="s">
         <v>204</v>
-      </c>
-      <c r="B62" t="s">
-        <v>205</v>
-      </c>
-      <c r="C62" t="s">
-        <v>206</v>
-      </c>
-      <c r="D62" t="s">
-        <v>207</v>
       </c>
       <c r="E62" s="4">
         <v>36</v>
       </c>
       <c r="H62" s="6"/>
       <c r="J62" s="3"/>
-      <c r="L62" s="6"/>
-    </row>
-    <row r="63" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K62" s="6"/>
+    </row>
+    <row r="63" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D63" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E63" s="4">
         <v>18</v>
       </c>
       <c r="H63" s="6"/>
       <c r="J63" s="3"/>
-      <c r="L63" s="6"/>
-    </row>
-    <row r="64" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K63" s="6"/>
+    </row>
+    <row r="64" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C64" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D64" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E64" s="4">
         <v>18</v>
       </c>
       <c r="H64" s="6"/>
       <c r="J64" s="3"/>
-      <c r="L64" s="6"/>
-    </row>
-    <row r="65" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K64" s="6"/>
+    </row>
+    <row r="65" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C65" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D65" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E65" s="4">
         <v>13</v>
       </c>
       <c r="H65" s="6"/>
       <c r="J65" s="3"/>
-      <c r="L65" s="6"/>
-    </row>
-    <row r="66" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K65" s="6"/>
+    </row>
+    <row r="66" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B66" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C66" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D66" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E66" s="4">
         <v>37</v>
       </c>
       <c r="H66" s="6"/>
       <c r="J66" s="3"/>
-      <c r="L66" s="6"/>
-    </row>
-    <row r="67" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K66" s="6"/>
+    </row>
+    <row r="67" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B67" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C67" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D67" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E67" s="4">
         <v>34</v>
       </c>
       <c r="H67" s="6"/>
       <c r="J67" s="3"/>
-      <c r="L67" s="6"/>
-    </row>
-    <row r="68" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K67" s="6"/>
+    </row>
+    <row r="68" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B68" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C68" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D68" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E68" s="4">
         <v>38</v>
       </c>
       <c r="H68" s="6"/>
       <c r="J68" s="3"/>
-      <c r="L68" s="6"/>
-    </row>
-    <row r="69" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K68" s="6"/>
+    </row>
+    <row r="69" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B69" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C69" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D69" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E69" s="4">
         <v>27</v>
       </c>
       <c r="H69" s="6"/>
       <c r="J69" s="3"/>
-      <c r="L69" s="6"/>
-    </row>
-    <row r="70" spans="1:12" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K69" s="6"/>
+    </row>
+    <row r="70" spans="1:11" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E70" s="6"/>
       <c r="H70" s="6"/>
       <c r="J70" s="3"/>
-      <c r="L70" s="6"/>
+      <c r="K70" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
